--- a/STR Loss.xlsx
+++ b/STR Loss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Saif\Activation\Data\STR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FBB5BB-49E7-4903-876B-06718ECEA0F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E36972-F548-4579-85F5-0AA169700D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{2FD34A2B-33D9-4773-B5D0-6D2681A7759A}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="58" r:id="rId3"/>
+    <pivotCache cacheId="60" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="244">
   <si>
     <t xml:space="preserve">Teleopti ID </t>
   </si>
@@ -650,6 +650,141 @@
   </si>
   <si>
     <t>Karim Fouad</t>
+  </si>
+  <si>
+    <t>IBS.Ahmed.344893</t>
+  </si>
+  <si>
+    <t>ibs.eman.378738</t>
+  </si>
+  <si>
+    <t>ibs.eman.422564</t>
+  </si>
+  <si>
+    <t>ibs.eriny.422556</t>
+  </si>
+  <si>
+    <t>IBS.Esraa.282826</t>
+  </si>
+  <si>
+    <t>ibs.esraa.418876</t>
+  </si>
+  <si>
+    <t>ibs.esraa.422562</t>
+  </si>
+  <si>
+    <t>IBS.Islam.272968</t>
+  </si>
+  <si>
+    <t>ibs.nada.422565</t>
+  </si>
+  <si>
+    <t>IBS.Nadeen.299861</t>
+  </si>
+  <si>
+    <t>ibs.sama.377180</t>
+  </si>
+  <si>
+    <t>IBS.Sara.197942</t>
+  </si>
+  <si>
+    <t>ibs.toka.213125</t>
+  </si>
+  <si>
+    <t>ibs.waad.422576</t>
+  </si>
+  <si>
+    <t>ibs.dalia.422664</t>
+  </si>
+  <si>
+    <t>ibs.hebatalah.422534</t>
+  </si>
+  <si>
+    <t>ibs.hesham.422567</t>
+  </si>
+  <si>
+    <t>ibs.islam.422578</t>
+  </si>
+  <si>
+    <t>ibs.mahmoud.422554</t>
+  </si>
+  <si>
+    <t>IBS.Mohamed.309895</t>
+  </si>
+  <si>
+    <t>IBS.Salma.338555</t>
+  </si>
+  <si>
+    <t>ibs.sara.422574</t>
+  </si>
+  <si>
+    <t>Ahmed Abd Elhmed Mustafa Abd Elhmed</t>
+  </si>
+  <si>
+    <t>Eman Ali Ragab Abdelalim</t>
+  </si>
+  <si>
+    <t>Eman Mohamed Emam Ahmed</t>
+  </si>
+  <si>
+    <t>Eriny Hany Faik hanna</t>
+  </si>
+  <si>
+    <t>Esraa Mustafa Ahmed Megahed</t>
+  </si>
+  <si>
+    <t>Esraa Abdel Hamied Gamal Abdel Fatah</t>
+  </si>
+  <si>
+    <t>Esraa Sayed Ebrahiem Abdel Rady</t>
+  </si>
+  <si>
+    <t>Islam Khaled Rasahd Ali</t>
+  </si>
+  <si>
+    <t>Nada Salman Ebrahiem Ragab</t>
+  </si>
+  <si>
+    <t>Nadeen Osama Ahmed Mohamed</t>
+  </si>
+  <si>
+    <t>Sama Salah Shabaan Abdel Hameed</t>
+  </si>
+  <si>
+    <t>Sara Mohmed Moamen Khalel</t>
+  </si>
+  <si>
+    <t>Toka Saber Helmy Ahmed</t>
+  </si>
+  <si>
+    <t>Waad Salem Abdelrahman Mohamed</t>
+  </si>
+  <si>
+    <t>Dalia Mamdouh Siddek Hammad</t>
+  </si>
+  <si>
+    <t>Hebatallah Zaki Mohamed Wahman</t>
+  </si>
+  <si>
+    <t>Hesham Mohamed Hussien Hammad</t>
+  </si>
+  <si>
+    <t>Islam Ashraf Qaoud Darder</t>
+  </si>
+  <si>
+    <t>Mahmoud Adel Mohamed El Shahat</t>
+  </si>
+  <si>
+    <t>Mohamed Sobhy Mohamed Abdelazem</t>
+  </si>
+  <si>
+    <t>Salma Ahmed Saber Mohamed</t>
+  </si>
+  <si>
+    <t>Sara Harby Youssef Mohamed</t>
+  </si>
+  <si>
+    <t>Samira - OJT</t>
   </si>
 </sst>
 </file>
@@ -678,7 +813,7 @@
       <name val="Poppins"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -691,8 +826,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -715,11 +856,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -739,6 +891,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6195,7 +6353,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9513112-8034-4B63-8D9B-FD9D9C7B9812}" name="PivotTable5" cacheId="58" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9513112-8034-4B63-8D9B-FD9D9C7B9812}" name="PivotTable5" cacheId="60" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="26">
     <pivotField showAll="0"/>
@@ -6948,7 +7106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D298249-7ED6-40BA-9E05-5DFDB3CB7DCD}">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
@@ -8596,6 +8754,446 @@
         <v>155</v>
       </c>
       <c r="F82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>344893</v>
+      </c>
+      <c r="B83" s="2">
+        <v>617551</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>378738</v>
+      </c>
+      <c r="B84" s="2">
+        <v>618135</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>422564</v>
+      </c>
+      <c r="B85" s="2">
+        <v>617932</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>422556</v>
+      </c>
+      <c r="B86" s="2">
+        <v>617890</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>282826</v>
+      </c>
+      <c r="B87" s="2">
+        <v>617629</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>418876</v>
+      </c>
+      <c r="B88" s="2">
+        <v>618134</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>422562</v>
+      </c>
+      <c r="B89" s="2">
+        <v>617901</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>272968</v>
+      </c>
+      <c r="B90" s="2">
+        <v>617777</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>422565</v>
+      </c>
+      <c r="B91" s="2">
+        <v>617965</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>299861</v>
+      </c>
+      <c r="B92" s="2">
+        <v>617696</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>377180</v>
+      </c>
+      <c r="B93" s="2">
+        <v>617978</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>197942</v>
+      </c>
+      <c r="B94" s="2">
+        <v>617481</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>213125</v>
+      </c>
+      <c r="B95" s="2">
+        <v>617503</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>422576</v>
+      </c>
+      <c r="B96" s="2">
+        <v>618031</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>422664</v>
+      </c>
+      <c r="B97" s="2">
+        <v>618111</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>422534</v>
+      </c>
+      <c r="B98" s="2">
+        <v>617805</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>422567</v>
+      </c>
+      <c r="B99" s="2">
+        <v>617994</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>422578</v>
+      </c>
+      <c r="B100" s="2">
+        <v>618107</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>422554</v>
+      </c>
+      <c r="B101" s="2">
+        <v>617856</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>309895</v>
+      </c>
+      <c r="B102" s="2">
+        <v>617761</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>338555</v>
+      </c>
+      <c r="B103" s="2">
+        <v>617591</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
+        <v>422574</v>
+      </c>
+      <c r="B104" s="2">
+        <v>617995</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/STR Loss.xlsx
+++ b/STR Loss.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Saif\Activation\Data\STR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E36972-F548-4579-85F5-0AA169700D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0E7DF-BF3D-46EB-BF92-38883BA346CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{2FD34A2B-33D9-4773-B5D0-6D2681A7759A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId1"/>
-    <sheet name="Sep Updated" sheetId="1" r:id="rId2"/>
+    <sheet name="OCT Updated" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sep Updated'!$A$1:$E$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OCT Updated'!$A$1:$E$82</definedName>
     <definedName name="Slicer_Status">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="60" r:id="rId3"/>
+    <pivotCache cacheId="63" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1441,7 +1441,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mahmoud Seif Mohamed" refreshedDate="46281.729949652778" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="171" xr:uid="{90E536DA-20C6-4A62-B9E9-4FE74DB8F431}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:E1048576" sheet="Sep Updated"/>
+    <worksheetSource ref="A1:E1048576" sheet="OCT Updated"/>
   </cacheSource>
   <cacheFields count="26">
     <cacheField name="Teleopti ID " numFmtId="0">
@@ -6353,7 +6353,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9513112-8034-4B63-8D9B-FD9D9C7B9812}" name="PivotTable5" cacheId="60" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9513112-8034-4B63-8D9B-FD9D9C7B9812}" name="PivotTable5" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:F19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="26">
     <pivotField showAll="0"/>
